--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,9 @@
     <t>['50']</t>
   </si>
   <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -851,6 +854,9 @@
   </si>
   <si>
     <t>['9', '77', '88']</t>
+  </si>
+  <si>
+    <t>['6', '65']</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1468,7 +1474,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2167,7 +2173,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2498,7 +2504,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2988,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ9">
         <v>0.6</v>
@@ -3322,7 +3328,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3734,7 +3740,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3940,7 +3946,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4146,7 +4152,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4558,7 +4564,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5176,7 +5182,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5254,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5588,7 +5594,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5794,7 +5800,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -5875,7 +5881,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR23">
         <v>2.53</v>
@@ -6206,7 +6212,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6618,7 +6624,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6824,7 +6830,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7030,7 +7036,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8060,7 +8066,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8138,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34">
         <v>0.8</v>
@@ -8266,7 +8272,7 @@
         <v>87</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -8472,7 +8478,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9502,7 +9508,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9708,7 +9714,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10326,7 +10332,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10819,7 +10825,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ47">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR47">
         <v>1.76</v>
@@ -10944,7 +10950,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11150,7 +11156,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11356,7 +11362,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11562,7 +11568,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12592,7 +12598,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13004,7 +13010,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13085,7 +13091,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ58">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR58">
         <v>0.9399999999999999</v>
@@ -13210,7 +13216,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13288,7 +13294,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ59">
         <v>1.5</v>
@@ -13622,7 +13628,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14446,7 +14452,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15064,7 +15070,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15270,7 +15276,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16094,7 +16100,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16175,7 +16181,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR73">
         <v>1.73</v>
@@ -16300,7 +16306,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16378,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
         <v>0.1</v>
@@ -16712,7 +16718,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -18154,7 +18160,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18232,7 +18238,7 @@
         <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ83">
         <v>1.8</v>
@@ -18772,7 +18778,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -18853,7 +18859,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR86">
         <v>1.86</v>
@@ -19802,7 +19808,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20008,7 +20014,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20420,7 +20426,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20832,7 +20838,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21038,7 +21044,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21322,7 +21328,7 @@
         <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ98">
         <v>1.5</v>
@@ -21450,7 +21456,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21531,7 +21537,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ99">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR99">
         <v>1.16</v>
@@ -21656,7 +21662,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21862,7 +21868,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22892,7 +22898,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23098,7 +23104,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23304,7 +23310,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23716,7 +23722,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24334,7 +24340,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24540,7 +24546,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
@@ -24827,7 +24833,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ115">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR115">
         <v>2.07</v>
@@ -25570,7 +25576,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26060,7 +26066,7 @@
         <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ121">
         <v>0.45</v>
@@ -26188,7 +26194,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26806,7 +26812,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27218,7 +27224,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27424,7 +27430,7 @@
         <v>183</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q128">
         <v>2.5</v>
@@ -27630,7 +27636,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27708,7 +27714,7 @@
         <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ129">
         <v>1.3</v>
@@ -27836,7 +27842,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28248,7 +28254,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28535,7 +28541,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ133">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28660,7 +28666,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29072,7 +29078,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -30102,7 +30108,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30514,7 +30520,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30720,7 +30726,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31132,7 +31138,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31210,7 +31216,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31419,7 +31425,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ147">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR147">
         <v>1.75</v>
@@ -31544,7 +31550,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31750,7 +31756,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32368,7 +32374,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32780,7 +32786,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32986,7 +32992,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33192,7 +33198,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33604,7 +33610,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34016,7 +34022,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34222,7 +34228,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34585,6 +34591,212 @@
       </c>
       <c r="BP162">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7453587</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45668.5</v>
+      </c>
+      <c r="F163">
+        <v>21</v>
+      </c>
+      <c r="G163" t="s">
+        <v>77</v>
+      </c>
+      <c r="H163" t="s">
+        <v>81</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>3</v>
+      </c>
+      <c r="O163" t="s">
+        <v>207</v>
+      </c>
+      <c r="P163" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q163">
+        <v>2.45</v>
+      </c>
+      <c r="R163">
+        <v>2.3</v>
+      </c>
+      <c r="S163">
+        <v>3.5</v>
+      </c>
+      <c r="T163">
+        <v>1.25</v>
+      </c>
+      <c r="U163">
+        <v>3.6</v>
+      </c>
+      <c r="V163">
+        <v>2.1</v>
+      </c>
+      <c r="W163">
+        <v>1.63</v>
+      </c>
+      <c r="X163">
+        <v>4.6</v>
+      </c>
+      <c r="Y163">
+        <v>1.17</v>
+      </c>
+      <c r="Z163">
+        <v>2</v>
+      </c>
+      <c r="AA163">
+        <v>3.75</v>
+      </c>
+      <c r="AB163">
+        <v>3.4</v>
+      </c>
+      <c r="AC163">
+        <v>1.01</v>
+      </c>
+      <c r="AD163">
+        <v>13</v>
+      </c>
+      <c r="AE163">
+        <v>1.17</v>
+      </c>
+      <c r="AF163">
+        <v>5</v>
+      </c>
+      <c r="AG163">
+        <v>1.49</v>
+      </c>
+      <c r="AH163">
+        <v>2.51</v>
+      </c>
+      <c r="AI163">
+        <v>1.46</v>
+      </c>
+      <c r="AJ163">
+        <v>2.55</v>
+      </c>
+      <c r="AK163">
+        <v>1.32</v>
+      </c>
+      <c r="AL163">
+        <v>1.26</v>
+      </c>
+      <c r="AM163">
+        <v>1.75</v>
+      </c>
+      <c r="AN163">
+        <v>1.6</v>
+      </c>
+      <c r="AO163">
+        <v>0.5</v>
+      </c>
+      <c r="AP163">
+        <v>1.45</v>
+      </c>
+      <c r="AQ163">
+        <v>0.73</v>
+      </c>
+      <c r="AR163">
+        <v>1.85</v>
+      </c>
+      <c r="AS163">
+        <v>1.33</v>
+      </c>
+      <c r="AT163">
+        <v>3.18</v>
+      </c>
+      <c r="AU163">
+        <v>6</v>
+      </c>
+      <c r="AV163">
+        <v>4</v>
+      </c>
+      <c r="AW163">
+        <v>20</v>
+      </c>
+      <c r="AX163">
+        <v>5</v>
+      </c>
+      <c r="AY163">
+        <v>32</v>
+      </c>
+      <c r="AZ163">
+        <v>10</v>
+      </c>
+      <c r="BA163">
+        <v>10</v>
+      </c>
+      <c r="BB163">
+        <v>1</v>
+      </c>
+      <c r="BC163">
+        <v>11</v>
+      </c>
+      <c r="BD163">
+        <v>1.76</v>
+      </c>
+      <c r="BE163">
+        <v>6.75</v>
+      </c>
+      <c r="BF163">
+        <v>2.28</v>
+      </c>
+      <c r="BG163">
+        <v>1.24</v>
+      </c>
+      <c r="BH163">
+        <v>3.55</v>
+      </c>
+      <c r="BI163">
+        <v>1.42</v>
+      </c>
+      <c r="BJ163">
+        <v>2.65</v>
+      </c>
+      <c r="BK163">
+        <v>1.68</v>
+      </c>
+      <c r="BL163">
+        <v>2.02</v>
+      </c>
+      <c r="BM163">
+        <v>2.07</v>
+      </c>
+      <c r="BN163">
+        <v>1.67</v>
+      </c>
+      <c r="BO163">
+        <v>2.65</v>
+      </c>
+      <c r="BP163">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="284">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['48', '84']</t>
   </si>
   <si>
+    <t>['1']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -805,9 +808,6 @@
     <t>['36', '45+3']</t>
   </si>
   <si>
-    <t>['1']</t>
-  </si>
-  <si>
     <t>['42', '47']</t>
   </si>
   <si>
@@ -862,7 +862,10 @@
     <t>['6', '65']</t>
   </si>
   <si>
-    <t>['59', '63']</t>
+    <t>['59', '62']</t>
+  </si>
+  <si>
+    <t>['10', '41', '79']</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1480,7 +1483,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1561,7 +1564,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1764,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3">
         <v>1.18</v>
@@ -1970,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ4">
         <v>0.73</v>
@@ -2176,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ5">
         <v>0.73</v>
@@ -2510,7 +2513,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2591,7 +2594,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2797,7 +2800,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3334,7 +3337,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3746,7 +3749,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3952,7 +3955,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4158,7 +4161,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4236,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15">
         <v>0.45</v>
@@ -4445,7 +4448,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ16">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4570,7 +4573,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4857,7 +4860,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -5060,7 +5063,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19">
         <v>0.45</v>
@@ -5188,7 +5191,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5472,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
         <v>0.73</v>
@@ -5600,7 +5603,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5681,7 +5684,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ22">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -5806,7 +5809,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6093,7 +6096,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR24">
         <v>1.65</v>
@@ -6218,7 +6221,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6296,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25">
         <v>0.1</v>
@@ -6630,7 +6633,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6708,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ27">
         <v>1.4</v>
@@ -6836,7 +6839,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7042,7 +7045,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7329,7 +7332,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR30">
         <v>2.35</v>
@@ -8072,7 +8075,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8278,7 +8281,7 @@
         <v>87</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -8359,7 +8362,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR35">
         <v>2.22</v>
@@ -8484,7 +8487,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8562,10 +8565,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ36">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -9514,7 +9517,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9720,7 +9723,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9798,7 +9801,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -10338,7 +10341,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10419,7 +10422,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10956,7 +10959,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11034,7 +11037,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ48">
         <v>0.7</v>
@@ -11162,7 +11165,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11240,7 +11243,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ49">
         <v>1.4</v>
@@ -11368,7 +11371,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11449,7 +11452,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ50">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -11574,7 +11577,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11652,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ51">
         <v>0.7</v>
@@ -12479,7 +12482,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR55">
         <v>1.72</v>
@@ -12604,7 +12607,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12682,7 +12685,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ56">
         <v>1.4</v>
@@ -13016,7 +13019,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13094,7 +13097,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ58">
         <v>0.73</v>
@@ -13222,7 +13225,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13303,7 +13306,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13506,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60">
         <v>0.91</v>
@@ -13634,7 +13637,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13715,7 +13718,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>2.01</v>
@@ -14458,7 +14461,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14536,10 +14539,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR65">
         <v>1.79</v>
@@ -14745,7 +14748,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -14951,7 +14954,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR67">
         <v>1.91</v>
@@ -15076,7 +15079,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15282,7 +15285,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15360,7 +15363,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ69">
         <v>1.5</v>
@@ -16106,7 +16109,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16184,7 +16187,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ73">
         <v>0.73</v>
@@ -16312,7 +16315,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16724,7 +16727,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -17008,7 +17011,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ77">
         <v>0.91</v>
@@ -17214,7 +17217,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ78">
         <v>0.7</v>
@@ -17835,7 +17838,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ81">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR81">
         <v>0.89</v>
@@ -18038,7 +18041,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ82">
         <v>1.5</v>
@@ -18166,7 +18169,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18247,7 +18250,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ83">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -18450,7 +18453,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ84">
         <v>1.5</v>
@@ -18659,7 +18662,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ85">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR85">
         <v>1.67</v>
@@ -18784,7 +18787,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19071,7 +19074,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ87">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR87">
         <v>1.36</v>
@@ -19814,7 +19817,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20020,7 +20023,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20098,10 +20101,10 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR92">
         <v>1.14</v>
@@ -20432,7 +20435,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20844,7 +20847,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21050,7 +21053,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21462,7 +21465,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21668,7 +21671,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21749,7 +21752,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ100">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -21874,7 +21877,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22161,7 +22164,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR102">
         <v>1.86</v>
@@ -22364,7 +22367,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103">
         <v>0.91</v>
@@ -22570,7 +22573,7 @@
         <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
         <v>0.45</v>
@@ -22776,10 +22779,10 @@
         <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ105">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR105">
         <v>0.83</v>
@@ -22904,7 +22907,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -22985,7 +22988,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR106">
         <v>1.33</v>
@@ -23110,7 +23113,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23191,7 +23194,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ107">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR107">
         <v>1.5</v>
@@ -23316,7 +23319,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23394,7 +23397,7 @@
         <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108">
         <v>0.73</v>
@@ -23728,7 +23731,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23806,7 +23809,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ110">
         <v>1.5</v>
@@ -24346,7 +24349,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24424,10 +24427,10 @@
         <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ113">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -24552,7 +24555,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
@@ -25582,7 +25585,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25866,10 +25869,10 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ120">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR120">
         <v>1.64</v>
@@ -26200,7 +26203,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26281,7 +26284,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR122">
         <v>1.47</v>
@@ -26818,7 +26821,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27230,7 +27233,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27308,7 +27311,7 @@
         <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ127">
         <v>0.6</v>
@@ -27436,7 +27439,7 @@
         <v>183</v>
       </c>
       <c r="P128" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="Q128">
         <v>2.5</v>
@@ -27517,7 +27520,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27723,7 +27726,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ129">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR129">
         <v>1.82</v>
@@ -28341,7 +28344,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ132">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28956,7 +28959,7 @@
         <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
         <v>1.18</v>
@@ -29162,7 +29165,7 @@
         <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ136">
         <v>0.1</v>
@@ -29368,7 +29371,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>0.7</v>
@@ -29577,7 +29580,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ138">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -29780,7 +29783,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ139">
         <v>0.7</v>
@@ -30526,7 +30529,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -31225,7 +31228,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR146">
         <v>1.85</v>
@@ -31634,10 +31637,10 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ148">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR148">
         <v>1.11</v>
@@ -31840,7 +31843,7 @@
         <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ149">
         <v>0.45</v>
@@ -32255,7 +32258,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ151">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR151">
         <v>1.23</v>
@@ -32461,7 +32464,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ152">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -32664,7 +32667,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ153">
         <v>0.73</v>
@@ -34312,7 +34315,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ161">
         <v>1.5</v>
@@ -34533,22 +34536,22 @@
         <v>2.25</v>
       </c>
       <c r="AU162">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV162">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW162">
+        <v>5</v>
+      </c>
+      <c r="AX162">
         <v>8</v>
       </c>
-      <c r="AX162">
-        <v>14</v>
-      </c>
       <c r="AY162">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ162">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA162">
         <v>3</v>
@@ -34739,19 +34742,19 @@
         <v>3.18</v>
       </c>
       <c r="AU163">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV163">
         <v>4</v>
       </c>
       <c r="AW163">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AX163">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY163">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AZ163">
         <v>10</v>
@@ -34945,22 +34948,22 @@
         <v>3</v>
       </c>
       <c r="AU164">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV164">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW164">
+        <v>4</v>
+      </c>
+      <c r="AX164">
         <v>7</v>
       </c>
-      <c r="AX164">
-        <v>15</v>
-      </c>
       <c r="AY164">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ164">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA164">
         <v>2</v>
@@ -35151,16 +35154,16 @@
         <v>3.19</v>
       </c>
       <c r="AU165">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV165">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW165">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX165">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY165">
         <v>9</v>
@@ -35215,6 +35218,830 @@
       </c>
       <c r="BP165">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7453586</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45669.39583333334</v>
+      </c>
+      <c r="F166">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>72</v>
+      </c>
+      <c r="H166" t="s">
+        <v>82</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>2</v>
+      </c>
+      <c r="O166" t="s">
+        <v>209</v>
+      </c>
+      <c r="P166" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q166">
+        <v>4.2</v>
+      </c>
+      <c r="R166">
+        <v>2.25</v>
+      </c>
+      <c r="S166">
+        <v>2.25</v>
+      </c>
+      <c r="T166">
+        <v>1.31</v>
+      </c>
+      <c r="U166">
+        <v>3.1</v>
+      </c>
+      <c r="V166">
+        <v>2.4</v>
+      </c>
+      <c r="W166">
+        <v>1.5</v>
+      </c>
+      <c r="X166">
+        <v>5.75</v>
+      </c>
+      <c r="Y166">
+        <v>1.12</v>
+      </c>
+      <c r="Z166">
+        <v>3.9</v>
+      </c>
+      <c r="AA166">
+        <v>3.85</v>
+      </c>
+      <c r="AB166">
+        <v>1.75</v>
+      </c>
+      <c r="AC166">
+        <v>1.03</v>
+      </c>
+      <c r="AD166">
+        <v>15</v>
+      </c>
+      <c r="AE166">
+        <v>1.21</v>
+      </c>
+      <c r="AF166">
+        <v>4.25</v>
+      </c>
+      <c r="AG166">
+        <v>1.65</v>
+      </c>
+      <c r="AH166">
+        <v>2.1</v>
+      </c>
+      <c r="AI166">
+        <v>1.65</v>
+      </c>
+      <c r="AJ166">
+        <v>2.1</v>
+      </c>
+      <c r="AK166">
+        <v>2</v>
+      </c>
+      <c r="AL166">
+        <v>1.25</v>
+      </c>
+      <c r="AM166">
+        <v>1.21</v>
+      </c>
+      <c r="AN166">
+        <v>1.1</v>
+      </c>
+      <c r="AO166">
+        <v>1.5</v>
+      </c>
+      <c r="AP166">
+        <v>1.09</v>
+      </c>
+      <c r="AQ166">
+        <v>1.45</v>
+      </c>
+      <c r="AR166">
+        <v>1.26</v>
+      </c>
+      <c r="AS166">
+        <v>1.22</v>
+      </c>
+      <c r="AT166">
+        <v>2.48</v>
+      </c>
+      <c r="AU166">
+        <v>8</v>
+      </c>
+      <c r="AV166">
+        <v>3</v>
+      </c>
+      <c r="AW166">
+        <v>6</v>
+      </c>
+      <c r="AX166">
+        <v>8</v>
+      </c>
+      <c r="AY166">
+        <v>17</v>
+      </c>
+      <c r="AZ166">
+        <v>13</v>
+      </c>
+      <c r="BA166">
+        <v>4</v>
+      </c>
+      <c r="BB166">
+        <v>6</v>
+      </c>
+      <c r="BC166">
+        <v>10</v>
+      </c>
+      <c r="BD166">
+        <v>2.7</v>
+      </c>
+      <c r="BE166">
+        <v>7</v>
+      </c>
+      <c r="BF166">
+        <v>1.52</v>
+      </c>
+      <c r="BG166">
+        <v>1.21</v>
+      </c>
+      <c r="BH166">
+        <v>3.9</v>
+      </c>
+      <c r="BI166">
+        <v>1.38</v>
+      </c>
+      <c r="BJ166">
+        <v>2.8</v>
+      </c>
+      <c r="BK166">
+        <v>1.61</v>
+      </c>
+      <c r="BL166">
+        <v>2.15</v>
+      </c>
+      <c r="BM166">
+        <v>1.97</v>
+      </c>
+      <c r="BN166">
+        <v>1.74</v>
+      </c>
+      <c r="BO166">
+        <v>2.45</v>
+      </c>
+      <c r="BP166">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7454760</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45669.5</v>
+      </c>
+      <c r="F167">
+        <v>21</v>
+      </c>
+      <c r="G167" t="s">
+        <v>71</v>
+      </c>
+      <c r="H167" t="s">
+        <v>85</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167" t="s">
+        <v>87</v>
+      </c>
+      <c r="P167" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q167">
+        <v>3.6</v>
+      </c>
+      <c r="R167">
+        <v>2.2</v>
+      </c>
+      <c r="S167">
+        <v>2.6</v>
+      </c>
+      <c r="T167">
+        <v>1.33</v>
+      </c>
+      <c r="U167">
+        <v>3</v>
+      </c>
+      <c r="V167">
+        <v>2.55</v>
+      </c>
+      <c r="W167">
+        <v>1.46</v>
+      </c>
+      <c r="X167">
+        <v>6.25</v>
+      </c>
+      <c r="Y167">
+        <v>1.1</v>
+      </c>
+      <c r="Z167">
+        <v>3.3</v>
+      </c>
+      <c r="AA167">
+        <v>3.4</v>
+      </c>
+      <c r="AB167">
+        <v>2.05</v>
+      </c>
+      <c r="AC167">
+        <v>1.05</v>
+      </c>
+      <c r="AD167">
+        <v>9.5</v>
+      </c>
+      <c r="AE167">
+        <v>1.25</v>
+      </c>
+      <c r="AF167">
+        <v>3.7</v>
+      </c>
+      <c r="AG167">
+        <v>1.7</v>
+      </c>
+      <c r="AH167">
+        <v>2.1</v>
+      </c>
+      <c r="AI167">
+        <v>1.66</v>
+      </c>
+      <c r="AJ167">
+        <v>2.05</v>
+      </c>
+      <c r="AK167">
+        <v>1.71</v>
+      </c>
+      <c r="AL167">
+        <v>1.27</v>
+      </c>
+      <c r="AM167">
+        <v>1.33</v>
+      </c>
+      <c r="AN167">
+        <v>1.2</v>
+      </c>
+      <c r="AO167">
+        <v>1.3</v>
+      </c>
+      <c r="AP167">
+        <v>1.18</v>
+      </c>
+      <c r="AQ167">
+        <v>1.27</v>
+      </c>
+      <c r="AR167">
+        <v>1.07</v>
+      </c>
+      <c r="AS167">
+        <v>1.17</v>
+      </c>
+      <c r="AT167">
+        <v>2.24</v>
+      </c>
+      <c r="AU167">
+        <v>4</v>
+      </c>
+      <c r="AV167">
+        <v>2</v>
+      </c>
+      <c r="AW167">
+        <v>5</v>
+      </c>
+      <c r="AX167">
+        <v>5</v>
+      </c>
+      <c r="AY167">
+        <v>12</v>
+      </c>
+      <c r="AZ167">
+        <v>9</v>
+      </c>
+      <c r="BA167">
+        <v>5</v>
+      </c>
+      <c r="BB167">
+        <v>1</v>
+      </c>
+      <c r="BC167">
+        <v>6</v>
+      </c>
+      <c r="BD167">
+        <v>1.98</v>
+      </c>
+      <c r="BE167">
+        <v>6.4</v>
+      </c>
+      <c r="BF167">
+        <v>1.98</v>
+      </c>
+      <c r="BG167">
+        <v>1.28</v>
+      </c>
+      <c r="BH167">
+        <v>3.2</v>
+      </c>
+      <c r="BI167">
+        <v>1.49</v>
+      </c>
+      <c r="BJ167">
+        <v>2.4</v>
+      </c>
+      <c r="BK167">
+        <v>1.81</v>
+      </c>
+      <c r="BL167">
+        <v>1.89</v>
+      </c>
+      <c r="BM167">
+        <v>2.25</v>
+      </c>
+      <c r="BN167">
+        <v>1.55</v>
+      </c>
+      <c r="BO167">
+        <v>2.9</v>
+      </c>
+      <c r="BP167">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7453583</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45669.60416666666</v>
+      </c>
+      <c r="F168">
+        <v>21</v>
+      </c>
+      <c r="G168" t="s">
+        <v>73</v>
+      </c>
+      <c r="H168" t="s">
+        <v>70</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>2</v>
+      </c>
+      <c r="K168">
+        <v>2</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>3</v>
+      </c>
+      <c r="N168">
+        <v>3</v>
+      </c>
+      <c r="O168" t="s">
+        <v>87</v>
+      </c>
+      <c r="P168" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q168">
+        <v>3.6</v>
+      </c>
+      <c r="R168">
+        <v>2.2</v>
+      </c>
+      <c r="S168">
+        <v>2.55</v>
+      </c>
+      <c r="T168">
+        <v>1.31</v>
+      </c>
+      <c r="U168">
+        <v>3.1</v>
+      </c>
+      <c r="V168">
+        <v>2.37</v>
+      </c>
+      <c r="W168">
+        <v>1.51</v>
+      </c>
+      <c r="X168">
+        <v>5.5</v>
+      </c>
+      <c r="Y168">
+        <v>1.12</v>
+      </c>
+      <c r="Z168">
+        <v>3.5</v>
+      </c>
+      <c r="AA168">
+        <v>3.3</v>
+      </c>
+      <c r="AB168">
+        <v>2.05</v>
+      </c>
+      <c r="AC168">
+        <v>1.05</v>
+      </c>
+      <c r="AD168">
+        <v>9.5</v>
+      </c>
+      <c r="AE168">
+        <v>1.22</v>
+      </c>
+      <c r="AF168">
+        <v>4</v>
+      </c>
+      <c r="AG168">
+        <v>1.79</v>
+      </c>
+      <c r="AH168">
+        <v>1.95</v>
+      </c>
+      <c r="AI168">
+        <v>1.57</v>
+      </c>
+      <c r="AJ168">
+        <v>2.25</v>
+      </c>
+      <c r="AK168">
+        <v>1.72</v>
+      </c>
+      <c r="AL168">
+        <v>1.28</v>
+      </c>
+      <c r="AM168">
+        <v>1.32</v>
+      </c>
+      <c r="AN168">
+        <v>1.8</v>
+      </c>
+      <c r="AO168">
+        <v>1.8</v>
+      </c>
+      <c r="AP168">
+        <v>1.64</v>
+      </c>
+      <c r="AQ168">
+        <v>1.91</v>
+      </c>
+      <c r="AR168">
+        <v>1.71</v>
+      </c>
+      <c r="AS168">
+        <v>1.6</v>
+      </c>
+      <c r="AT168">
+        <v>3.31</v>
+      </c>
+      <c r="AU168">
+        <v>6</v>
+      </c>
+      <c r="AV168">
+        <v>6</v>
+      </c>
+      <c r="AW168">
+        <v>7</v>
+      </c>
+      <c r="AX168">
+        <v>7</v>
+      </c>
+      <c r="AY168">
+        <v>16</v>
+      </c>
+      <c r="AZ168">
+        <v>14</v>
+      </c>
+      <c r="BA168">
+        <v>8</v>
+      </c>
+      <c r="BB168">
+        <v>5</v>
+      </c>
+      <c r="BC168">
+        <v>13</v>
+      </c>
+      <c r="BD168">
+        <v>2.2</v>
+      </c>
+      <c r="BE168">
+        <v>6.4</v>
+      </c>
+      <c r="BF168">
+        <v>1.81</v>
+      </c>
+      <c r="BG168">
+        <v>1.32</v>
+      </c>
+      <c r="BH168">
+        <v>3.05</v>
+      </c>
+      <c r="BI168">
+        <v>1.55</v>
+      </c>
+      <c r="BJ168">
+        <v>2.25</v>
+      </c>
+      <c r="BK168">
+        <v>1.9</v>
+      </c>
+      <c r="BL168">
+        <v>1.79</v>
+      </c>
+      <c r="BM168">
+        <v>2.4</v>
+      </c>
+      <c r="BN168">
+        <v>1.5</v>
+      </c>
+      <c r="BO168">
+        <v>3.15</v>
+      </c>
+      <c r="BP168">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7454759</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45669.63541666666</v>
+      </c>
+      <c r="F169">
+        <v>21</v>
+      </c>
+      <c r="G169" t="s">
+        <v>83</v>
+      </c>
+      <c r="H169" t="s">
+        <v>79</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169" t="s">
+        <v>94</v>
+      </c>
+      <c r="P169" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q169">
+        <v>2.7</v>
+      </c>
+      <c r="R169">
+        <v>2.2</v>
+      </c>
+      <c r="S169">
+        <v>3.3</v>
+      </c>
+      <c r="T169">
+        <v>1.33</v>
+      </c>
+      <c r="U169">
+        <v>3.1</v>
+      </c>
+      <c r="V169">
+        <v>2.5</v>
+      </c>
+      <c r="W169">
+        <v>1.46</v>
+      </c>
+      <c r="X169">
+        <v>6</v>
+      </c>
+      <c r="Y169">
+        <v>1.11</v>
+      </c>
+      <c r="Z169">
+        <v>2.15</v>
+      </c>
+      <c r="AA169">
+        <v>3.4</v>
+      </c>
+      <c r="AB169">
+        <v>3</v>
+      </c>
+      <c r="AC169">
+        <v>1.05</v>
+      </c>
+      <c r="AD169">
+        <v>9.5</v>
+      </c>
+      <c r="AE169">
+        <v>1.25</v>
+      </c>
+      <c r="AF169">
+        <v>3.8</v>
+      </c>
+      <c r="AG169">
+        <v>1.65</v>
+      </c>
+      <c r="AH169">
+        <v>2.15</v>
+      </c>
+      <c r="AI169">
+        <v>1.62</v>
+      </c>
+      <c r="AJ169">
+        <v>2.15</v>
+      </c>
+      <c r="AK169">
+        <v>1.38</v>
+      </c>
+      <c r="AL169">
+        <v>1.28</v>
+      </c>
+      <c r="AM169">
+        <v>1.62</v>
+      </c>
+      <c r="AN169">
+        <v>1.5</v>
+      </c>
+      <c r="AO169">
+        <v>1</v>
+      </c>
+      <c r="AP169">
+        <v>1.64</v>
+      </c>
+      <c r="AQ169">
+        <v>0.9</v>
+      </c>
+      <c r="AR169">
+        <v>1.59</v>
+      </c>
+      <c r="AS169">
+        <v>1.28</v>
+      </c>
+      <c r="AT169">
+        <v>2.87</v>
+      </c>
+      <c r="AU169">
+        <v>8</v>
+      </c>
+      <c r="AV169">
+        <v>6</v>
+      </c>
+      <c r="AW169">
+        <v>12</v>
+      </c>
+      <c r="AX169">
+        <v>5</v>
+      </c>
+      <c r="AY169">
+        <v>24</v>
+      </c>
+      <c r="AZ169">
+        <v>11</v>
+      </c>
+      <c r="BA169">
+        <v>7</v>
+      </c>
+      <c r="BB169">
+        <v>4</v>
+      </c>
+      <c r="BC169">
+        <v>11</v>
+      </c>
+      <c r="BD169">
+        <v>1.71</v>
+      </c>
+      <c r="BE169">
+        <v>6.75</v>
+      </c>
+      <c r="BF169">
+        <v>2.38</v>
+      </c>
+      <c r="BG169">
+        <v>1.27</v>
+      </c>
+      <c r="BH169">
+        <v>3.3</v>
+      </c>
+      <c r="BI169">
+        <v>1.48</v>
+      </c>
+      <c r="BJ169">
+        <v>2.45</v>
+      </c>
+      <c r="BK169">
+        <v>1.77</v>
+      </c>
+      <c r="BL169">
+        <v>1.93</v>
+      </c>
+      <c r="BM169">
+        <v>2.18</v>
+      </c>
+      <c r="BN169">
+        <v>1.58</v>
+      </c>
+      <c r="BO169">
+        <v>2.8</v>
+      </c>
+      <c r="BP169">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -35378,13 +35378,13 @@
         <v>13</v>
       </c>
       <c r="BA166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB166">
         <v>6</v>
       </c>
       <c r="BC166">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD166">
         <v>2.7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="288">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,9 @@
     <t>['1']</t>
   </si>
   <si>
+    <t>['19', '22', '77', '90+5']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -866,6 +869,15 @@
   </si>
   <si>
     <t>['10', '41', '79']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['15', '25']</t>
+  </si>
+  <si>
+    <t>['80', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1483,7 +1495,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1561,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2">
         <v>0.9</v>
@@ -1767,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3">
         <v>1.18</v>
@@ -2513,7 +2525,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3006,7 +3018,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ9">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3212,7 +3224,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ10">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3337,7 +3349,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3415,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>0.7</v>
@@ -3624,7 +3636,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ12">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3749,7 +3761,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3830,7 +3842,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ13">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3955,7 +3967,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4161,7 +4173,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4573,7 +4585,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4651,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ17">
         <v>1.5</v>
@@ -5063,7 +5075,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
         <v>0.45</v>
@@ -5191,7 +5203,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5603,7 +5615,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5809,7 +5821,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6221,7 +6233,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6302,7 +6314,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ25">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR25">
         <v>2.16</v>
@@ -6508,7 +6520,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ26">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6633,7 +6645,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6714,7 +6726,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ27">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR27">
         <v>0.45</v>
@@ -6839,7 +6851,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7045,7 +7057,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7123,7 +7135,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -7329,7 +7341,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ30">
         <v>1.45</v>
@@ -7538,7 +7550,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ31">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -7947,7 +7959,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ33">
         <v>0.7</v>
@@ -8075,7 +8087,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8281,7 +8293,7 @@
         <v>87</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -8487,7 +8499,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8565,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ36">
         <v>1.91</v>
@@ -8980,7 +8992,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ38">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9517,7 +9529,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9595,10 +9607,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
         <v>1.62</v>
@@ -9723,7 +9735,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10213,10 +10225,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ44">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR44">
         <v>1.89</v>
@@ -10341,7 +10353,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10419,7 +10431,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ45">
         <v>1.45</v>
@@ -10959,7 +10971,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11037,7 +11049,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ48">
         <v>0.7</v>
@@ -11165,7 +11177,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11246,7 +11258,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ49">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR49">
         <v>2.18</v>
@@ -11371,7 +11383,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11577,7 +11589,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12276,7 +12288,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ54">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR54">
         <v>1.56</v>
@@ -12479,7 +12491,7 @@
         <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ55">
         <v>0.9</v>
@@ -12607,7 +12619,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12688,7 +12700,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ56">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -13019,7 +13031,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13225,7 +13237,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13512,7 +13524,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ60">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
         <v>1.66</v>
@@ -13637,7 +13649,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13715,7 +13727,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -13921,10 +13933,10 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR62">
         <v>1.5</v>
@@ -14461,7 +14473,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15079,7 +15091,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15285,7 +15297,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15363,7 +15375,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ69">
         <v>1.5</v>
@@ -15572,7 +15584,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ70">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR70">
         <v>1.88</v>
@@ -15981,7 +15993,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ72">
         <v>0.73</v>
@@ -16109,7 +16121,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16315,7 +16327,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16396,7 +16408,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ74">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR74">
         <v>1.66</v>
@@ -16599,7 +16611,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75">
         <v>0.73</v>
@@ -16727,7 +16739,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -16808,7 +16820,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ76">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17011,10 +17023,10 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ77">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
         <v>1.23</v>
@@ -17426,7 +17438,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ79">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR79">
         <v>1.88</v>
@@ -17629,7 +17641,7 @@
         <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ80">
         <v>1.18</v>
@@ -18169,7 +18181,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18787,7 +18799,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19280,7 +19292,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ88">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR88">
         <v>1.14</v>
@@ -19483,7 +19495,7 @@
         <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ89">
         <v>0.45</v>
@@ -19692,7 +19704,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR90">
         <v>1.5</v>
@@ -19817,7 +19829,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20023,7 +20035,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20101,7 +20113,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ92">
         <v>0.9</v>
@@ -20435,7 +20447,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20513,7 +20525,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ94">
         <v>1.5</v>
@@ -20847,7 +20859,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20925,10 +20937,10 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ96">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21053,7 +21065,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21134,7 +21146,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ97">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21465,7 +21477,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21671,7 +21683,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21877,7 +21889,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -21955,7 +21967,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
         <v>1.18</v>
@@ -22370,7 +22382,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ103">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
         <v>1.64</v>
@@ -22907,7 +22919,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23113,7 +23125,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23319,7 +23331,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23397,7 +23409,7 @@
         <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>0.73</v>
@@ -23731,7 +23743,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24015,7 +24027,7 @@
         <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ111">
         <v>0.7</v>
@@ -24224,7 +24236,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ112">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR112">
         <v>1.71</v>
@@ -24349,7 +24361,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24555,7 +24567,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
@@ -24839,7 +24851,7 @@
         <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ115">
         <v>0.73</v>
@@ -25048,7 +25060,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ116">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR116">
         <v>1.18</v>
@@ -25254,7 +25266,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ117">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR117">
         <v>1.85</v>
@@ -25457,10 +25469,10 @@
         <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ118">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR118">
         <v>1.51</v>
@@ -25585,7 +25597,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26203,7 +26215,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26487,7 +26499,7 @@
         <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ123">
         <v>1.5</v>
@@ -26821,7 +26833,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -26902,7 +26914,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ125">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR125">
         <v>1.37</v>
@@ -27233,7 +27245,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27314,7 +27326,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ127">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR127">
         <v>0.92</v>
@@ -27645,7 +27657,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27851,7 +27863,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28263,7 +28275,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28341,7 +28353,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ132">
         <v>1.91</v>
@@ -28547,7 +28559,7 @@
         <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ133">
         <v>0.73</v>
@@ -28675,7 +28687,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28756,7 +28768,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ134">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR134">
         <v>1.76</v>
@@ -29087,7 +29099,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29168,7 +29180,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ136">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR136">
         <v>1.71</v>
@@ -29371,7 +29383,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ137">
         <v>0.7</v>
@@ -29577,7 +29589,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
         <v>1.45</v>
@@ -29992,7 +30004,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ140">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR140">
         <v>1.25</v>
@@ -30117,7 +30129,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30401,10 +30413,10 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ142">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR142">
         <v>2.07</v>
@@ -30529,7 +30541,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30735,7 +30747,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31019,10 +31031,10 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ145">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR145">
         <v>1.64</v>
@@ -31147,7 +31159,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31559,7 +31571,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31637,7 +31649,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ148">
         <v>1.45</v>
@@ -31765,7 +31777,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32383,7 +32395,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32795,7 +32807,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32876,7 +32888,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ154">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR154">
         <v>1.81</v>
@@ -33001,7 +33013,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33082,7 +33094,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ155">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -33207,7 +33219,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33285,7 +33297,7 @@
         <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ156">
         <v>0.7</v>
@@ -33491,7 +33503,7 @@
         <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
         <v>0.7</v>
@@ -33619,7 +33631,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33697,7 +33709,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ158">
         <v>1.18</v>
@@ -33906,7 +33918,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ159">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34031,7 +34043,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34112,7 +34124,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ160">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR160">
         <v>1.47</v>
@@ -34237,7 +34249,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34649,7 +34661,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35061,7 +35073,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35267,7 +35279,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35551,7 +35563,7 @@
         <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ167">
         <v>1.27</v>
@@ -35679,7 +35691,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36042,6 +36054,830 @@
       </c>
       <c r="BP169">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7453591</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45674.69791666666</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>85</v>
+      </c>
+      <c r="H170" t="s">
+        <v>76</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>2</v>
+      </c>
+      <c r="O170" t="s">
+        <v>115</v>
+      </c>
+      <c r="P170" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q170">
+        <v>2.55</v>
+      </c>
+      <c r="R170">
+        <v>2.2</v>
+      </c>
+      <c r="S170">
+        <v>3.6</v>
+      </c>
+      <c r="T170">
+        <v>1.33</v>
+      </c>
+      <c r="U170">
+        <v>3.1</v>
+      </c>
+      <c r="V170">
+        <v>2.5</v>
+      </c>
+      <c r="W170">
+        <v>1.46</v>
+      </c>
+      <c r="X170">
+        <v>6</v>
+      </c>
+      <c r="Y170">
+        <v>1.11</v>
+      </c>
+      <c r="Z170">
+        <v>2.05</v>
+      </c>
+      <c r="AA170">
+        <v>3.6</v>
+      </c>
+      <c r="AB170">
+        <v>3.3</v>
+      </c>
+      <c r="AC170">
+        <v>1.04</v>
+      </c>
+      <c r="AD170">
+        <v>10</v>
+      </c>
+      <c r="AE170">
+        <v>1.25</v>
+      </c>
+      <c r="AF170">
+        <v>3.95</v>
+      </c>
+      <c r="AG170">
+        <v>1.75</v>
+      </c>
+      <c r="AH170">
+        <v>2.08</v>
+      </c>
+      <c r="AI170">
+        <v>1.63</v>
+      </c>
+      <c r="AJ170">
+        <v>2.1</v>
+      </c>
+      <c r="AK170">
+        <v>1.32</v>
+      </c>
+      <c r="AL170">
+        <v>1.27</v>
+      </c>
+      <c r="AM170">
+        <v>1.72</v>
+      </c>
+      <c r="AN170">
+        <v>1.7</v>
+      </c>
+      <c r="AO170">
+        <v>0.91</v>
+      </c>
+      <c r="AP170">
+        <v>1.64</v>
+      </c>
+      <c r="AQ170">
+        <v>0.92</v>
+      </c>
+      <c r="AR170">
+        <v>1.54</v>
+      </c>
+      <c r="AS170">
+        <v>1.44</v>
+      </c>
+      <c r="AT170">
+        <v>2.98</v>
+      </c>
+      <c r="AU170">
+        <v>4</v>
+      </c>
+      <c r="AV170">
+        <v>5</v>
+      </c>
+      <c r="AW170">
+        <v>5</v>
+      </c>
+      <c r="AX170">
+        <v>7</v>
+      </c>
+      <c r="AY170">
+        <v>12</v>
+      </c>
+      <c r="AZ170">
+        <v>12</v>
+      </c>
+      <c r="BA170">
+        <v>6</v>
+      </c>
+      <c r="BB170">
+        <v>7</v>
+      </c>
+      <c r="BC170">
+        <v>13</v>
+      </c>
+      <c r="BD170">
+        <v>1.7</v>
+      </c>
+      <c r="BE170">
+        <v>6.75</v>
+      </c>
+      <c r="BF170">
+        <v>2.4</v>
+      </c>
+      <c r="BG170">
+        <v>1.28</v>
+      </c>
+      <c r="BH170">
+        <v>3.3</v>
+      </c>
+      <c r="BI170">
+        <v>1.49</v>
+      </c>
+      <c r="BJ170">
+        <v>2.4</v>
+      </c>
+      <c r="BK170">
+        <v>1.79</v>
+      </c>
+      <c r="BL170">
+        <v>1.9</v>
+      </c>
+      <c r="BM170">
+        <v>2.25</v>
+      </c>
+      <c r="BN170">
+        <v>1.55</v>
+      </c>
+      <c r="BO170">
+        <v>2.9</v>
+      </c>
+      <c r="BP170">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7453596</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F171">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>71</v>
+      </c>
+      <c r="H171" t="s">
+        <v>83</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
+        <v>87</v>
+      </c>
+      <c r="P171" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q171">
+        <v>3.5</v>
+      </c>
+      <c r="R171">
+        <v>2.1</v>
+      </c>
+      <c r="S171">
+        <v>3.2</v>
+      </c>
+      <c r="T171">
+        <v>1.44</v>
+      </c>
+      <c r="U171">
+        <v>2.63</v>
+      </c>
+      <c r="V171">
+        <v>3</v>
+      </c>
+      <c r="W171">
+        <v>1.36</v>
+      </c>
+      <c r="X171">
+        <v>9</v>
+      </c>
+      <c r="Y171">
+        <v>1.07</v>
+      </c>
+      <c r="Z171">
+        <v>2.68</v>
+      </c>
+      <c r="AA171">
+        <v>3.21</v>
+      </c>
+      <c r="AB171">
+        <v>2.39</v>
+      </c>
+      <c r="AC171">
+        <v>1.05</v>
+      </c>
+      <c r="AD171">
+        <v>8.91</v>
+      </c>
+      <c r="AE171">
+        <v>1.31</v>
+      </c>
+      <c r="AF171">
+        <v>3.32</v>
+      </c>
+      <c r="AG171">
+        <v>1.9</v>
+      </c>
+      <c r="AH171">
+        <v>1.98</v>
+      </c>
+      <c r="AI171">
+        <v>1.75</v>
+      </c>
+      <c r="AJ171">
+        <v>2</v>
+      </c>
+      <c r="AK171">
+        <v>1.53</v>
+      </c>
+      <c r="AL171">
+        <v>1.31</v>
+      </c>
+      <c r="AM171">
+        <v>1.41</v>
+      </c>
+      <c r="AN171">
+        <v>1.18</v>
+      </c>
+      <c r="AO171">
+        <v>0.6</v>
+      </c>
+      <c r="AP171">
+        <v>1.08</v>
+      </c>
+      <c r="AQ171">
+        <v>0.82</v>
+      </c>
+      <c r="AR171">
+        <v>1.08</v>
+      </c>
+      <c r="AS171">
+        <v>1.34</v>
+      </c>
+      <c r="AT171">
+        <v>2.42</v>
+      </c>
+      <c r="AU171">
+        <v>2</v>
+      </c>
+      <c r="AV171">
+        <v>6</v>
+      </c>
+      <c r="AW171">
+        <v>7</v>
+      </c>
+      <c r="AX171">
+        <v>10</v>
+      </c>
+      <c r="AY171">
+        <v>10</v>
+      </c>
+      <c r="AZ171">
+        <v>19</v>
+      </c>
+      <c r="BA171">
+        <v>3</v>
+      </c>
+      <c r="BB171">
+        <v>5</v>
+      </c>
+      <c r="BC171">
+        <v>8</v>
+      </c>
+      <c r="BD171">
+        <v>1.89</v>
+      </c>
+      <c r="BE171">
+        <v>6.4</v>
+      </c>
+      <c r="BF171">
+        <v>2.1</v>
+      </c>
+      <c r="BG171">
+        <v>1.33</v>
+      </c>
+      <c r="BH171">
+        <v>3</v>
+      </c>
+      <c r="BI171">
+        <v>1.56</v>
+      </c>
+      <c r="BJ171">
+        <v>2.23</v>
+      </c>
+      <c r="BK171">
+        <v>1.75</v>
+      </c>
+      <c r="BL171">
+        <v>1.95</v>
+      </c>
+      <c r="BM171">
+        <v>2.4</v>
+      </c>
+      <c r="BN171">
+        <v>1.49</v>
+      </c>
+      <c r="BO171">
+        <v>3.15</v>
+      </c>
+      <c r="BP171">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7453594</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45675.59375</v>
+      </c>
+      <c r="F172">
+        <v>22</v>
+      </c>
+      <c r="G172" t="s">
+        <v>79</v>
+      </c>
+      <c r="H172" t="s">
+        <v>74</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>3</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>2</v>
+      </c>
+      <c r="N172">
+        <v>3</v>
+      </c>
+      <c r="O172" t="s">
+        <v>159</v>
+      </c>
+      <c r="P172" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q172">
+        <v>3.4</v>
+      </c>
+      <c r="R172">
+        <v>2.3</v>
+      </c>
+      <c r="S172">
+        <v>2.88</v>
+      </c>
+      <c r="T172">
+        <v>1.33</v>
+      </c>
+      <c r="U172">
+        <v>3.25</v>
+      </c>
+      <c r="V172">
+        <v>2.5</v>
+      </c>
+      <c r="W172">
+        <v>1.5</v>
+      </c>
+      <c r="X172">
+        <v>6.5</v>
+      </c>
+      <c r="Y172">
+        <v>1.11</v>
+      </c>
+      <c r="Z172">
+        <v>2.85</v>
+      </c>
+      <c r="AA172">
+        <v>3.55</v>
+      </c>
+      <c r="AB172">
+        <v>2.3</v>
+      </c>
+      <c r="AC172">
+        <v>1.04</v>
+      </c>
+      <c r="AD172">
+        <v>13</v>
+      </c>
+      <c r="AE172">
+        <v>1.22</v>
+      </c>
+      <c r="AF172">
+        <v>4.08</v>
+      </c>
+      <c r="AG172">
+        <v>1.58</v>
+      </c>
+      <c r="AH172">
+        <v>2.33</v>
+      </c>
+      <c r="AI172">
+        <v>1.57</v>
+      </c>
+      <c r="AJ172">
+        <v>2.25</v>
+      </c>
+      <c r="AK172">
+        <v>1.6</v>
+      </c>
+      <c r="AL172">
+        <v>1.27</v>
+      </c>
+      <c r="AM172">
+        <v>1.41</v>
+      </c>
+      <c r="AN172">
+        <v>1.64</v>
+      </c>
+      <c r="AO172">
+        <v>1.4</v>
+      </c>
+      <c r="AP172">
+        <v>1.5</v>
+      </c>
+      <c r="AQ172">
+        <v>1.55</v>
+      </c>
+      <c r="AR172">
+        <v>1.56</v>
+      </c>
+      <c r="AS172">
+        <v>1.72</v>
+      </c>
+      <c r="AT172">
+        <v>3.28</v>
+      </c>
+      <c r="AU172">
+        <v>3</v>
+      </c>
+      <c r="AV172">
+        <v>11</v>
+      </c>
+      <c r="AW172">
+        <v>3</v>
+      </c>
+      <c r="AX172">
+        <v>4</v>
+      </c>
+      <c r="AY172">
+        <v>6</v>
+      </c>
+      <c r="AZ172">
+        <v>16</v>
+      </c>
+      <c r="BA172">
+        <v>2</v>
+      </c>
+      <c r="BB172">
+        <v>0</v>
+      </c>
+      <c r="BC172">
+        <v>2</v>
+      </c>
+      <c r="BD172">
+        <v>2.18</v>
+      </c>
+      <c r="BE172">
+        <v>6.5</v>
+      </c>
+      <c r="BF172">
+        <v>1.81</v>
+      </c>
+      <c r="BG172">
+        <v>1.28</v>
+      </c>
+      <c r="BH172">
+        <v>3.2</v>
+      </c>
+      <c r="BI172">
+        <v>1.49</v>
+      </c>
+      <c r="BJ172">
+        <v>2.4</v>
+      </c>
+      <c r="BK172">
+        <v>1.7</v>
+      </c>
+      <c r="BL172">
+        <v>2.05</v>
+      </c>
+      <c r="BM172">
+        <v>2.05</v>
+      </c>
+      <c r="BN172">
+        <v>1.7</v>
+      </c>
+      <c r="BO172">
+        <v>2.8</v>
+      </c>
+      <c r="BP172">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7453589</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45675.69791666666</v>
+      </c>
+      <c r="F173">
+        <v>22</v>
+      </c>
+      <c r="G173" t="s">
+        <v>70</v>
+      </c>
+      <c r="H173" t="s">
+        <v>72</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>2</v>
+      </c>
+      <c r="L173">
+        <v>4</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>6</v>
+      </c>
+      <c r="O173" t="s">
+        <v>210</v>
+      </c>
+      <c r="P173" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q173">
+        <v>1.5</v>
+      </c>
+      <c r="R173">
+        <v>3.2</v>
+      </c>
+      <c r="S173">
+        <v>11</v>
+      </c>
+      <c r="T173">
+        <v>1.18</v>
+      </c>
+      <c r="U173">
+        <v>4.5</v>
+      </c>
+      <c r="V173">
+        <v>1.83</v>
+      </c>
+      <c r="W173">
+        <v>1.83</v>
+      </c>
+      <c r="X173">
+        <v>3.75</v>
+      </c>
+      <c r="Y173">
+        <v>1.25</v>
+      </c>
+      <c r="Z173">
+        <v>1.15</v>
+      </c>
+      <c r="AA173">
+        <v>8.75</v>
+      </c>
+      <c r="AB173">
+        <v>15</v>
+      </c>
+      <c r="AC173">
+        <v>0</v>
+      </c>
+      <c r="AD173">
+        <v>0</v>
+      </c>
+      <c r="AE173">
+        <v>1.08</v>
+      </c>
+      <c r="AF173">
+        <v>7.29</v>
+      </c>
+      <c r="AG173">
+        <v>1.3</v>
+      </c>
+      <c r="AH173">
+        <v>3.33</v>
+      </c>
+      <c r="AI173">
+        <v>1.95</v>
+      </c>
+      <c r="AJ173">
+        <v>1.8</v>
+      </c>
+      <c r="AK173">
+        <v>1.02</v>
+      </c>
+      <c r="AL173">
+        <v>1.07</v>
+      </c>
+      <c r="AM173">
+        <v>5.25</v>
+      </c>
+      <c r="AN173">
+        <v>2.3</v>
+      </c>
+      <c r="AO173">
+        <v>0.1</v>
+      </c>
+      <c r="AP173">
+        <v>2.36</v>
+      </c>
+      <c r="AQ173">
+        <v>0.09</v>
+      </c>
+      <c r="AR173">
+        <v>2.04</v>
+      </c>
+      <c r="AS173">
+        <v>1.04</v>
+      </c>
+      <c r="AT173">
+        <v>3.08</v>
+      </c>
+      <c r="AU173">
+        <v>10</v>
+      </c>
+      <c r="AV173">
+        <v>4</v>
+      </c>
+      <c r="AW173">
+        <v>7</v>
+      </c>
+      <c r="AX173">
+        <v>10</v>
+      </c>
+      <c r="AY173">
+        <v>17</v>
+      </c>
+      <c r="AZ173">
+        <v>17</v>
+      </c>
+      <c r="BA173">
+        <v>5</v>
+      </c>
+      <c r="BB173">
+        <v>3</v>
+      </c>
+      <c r="BC173">
+        <v>8</v>
+      </c>
+      <c r="BD173">
+        <v>1.16</v>
+      </c>
+      <c r="BE173">
+        <v>9.5</v>
+      </c>
+      <c r="BF173">
+        <v>5.4</v>
+      </c>
+      <c r="BG173">
+        <v>1.22</v>
+      </c>
+      <c r="BH173">
+        <v>3.8</v>
+      </c>
+      <c r="BI173">
+        <v>1.38</v>
+      </c>
+      <c r="BJ173">
+        <v>2.8</v>
+      </c>
+      <c r="BK173">
+        <v>1.77</v>
+      </c>
+      <c r="BL173">
+        <v>1.93</v>
+      </c>
+      <c r="BM173">
+        <v>1.95</v>
+      </c>
+      <c r="BN173">
+        <v>1.74</v>
+      </c>
+      <c r="BO173">
+        <v>2.43</v>
+      </c>
+      <c r="BP173">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,12 @@
     <t>['19', '22', '77', '90+5']</t>
   </si>
   <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['15', '57', '90+7']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -878,6 +884,15 @@
   </si>
   <si>
     <t>['80', '90+2']</t>
+  </si>
+  <si>
+    <t>['62', '90+3']</t>
+  </si>
+  <si>
+    <t>['42', '62']</t>
+  </si>
+  <si>
+    <t>['23', '36']</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1495,7 +1510,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1988,7 +2003,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2400,7 +2415,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ6">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2525,7 +2540,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2603,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ7">
         <v>1.27</v>
@@ -3221,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10">
         <v>0.09</v>
@@ -3349,7 +3364,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3430,7 +3445,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3761,7 +3776,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3839,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
         <v>0.92</v>
@@ -3967,7 +3982,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4045,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4173,7 +4188,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4585,7 +4600,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5203,7 +5218,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5490,7 +5505,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ21">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR21">
         <v>1.37</v>
@@ -5615,7 +5630,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5821,7 +5836,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -5899,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ23">
         <v>0.73</v>
@@ -6233,7 +6248,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6517,7 +6532,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ26">
         <v>0.92</v>
@@ -6645,7 +6660,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6851,7 +6866,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -6929,7 +6944,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -7057,7 +7072,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7138,7 +7153,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR29">
         <v>0.96</v>
@@ -7753,10 +7768,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7962,7 +7977,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ33">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR33">
         <v>1.52</v>
@@ -8087,7 +8102,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8168,7 +8183,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ34">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR34">
         <v>1.74</v>
@@ -8293,7 +8308,7 @@
         <v>87</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -8371,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ35">
         <v>0.9</v>
@@ -8499,7 +8514,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8783,7 +8798,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ37">
         <v>1.18</v>
@@ -9404,7 +9419,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ40">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -9529,7 +9544,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9735,7 +9750,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10022,7 +10037,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10353,7 +10368,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10637,10 +10652,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ46">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR46">
         <v>1.58</v>
@@ -10843,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47">
         <v>0.73</v>
@@ -10971,7 +10986,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11052,7 +11067,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ48">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11177,7 +11192,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11383,7 +11398,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11461,7 +11476,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ50">
         <v>1.91</v>
@@ -11589,7 +11604,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11670,7 +11685,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ51">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR51">
         <v>1.42</v>
@@ -11873,7 +11888,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ52">
         <v>1.18</v>
@@ -12079,10 +12094,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ53">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR53">
         <v>0.82</v>
@@ -12619,7 +12634,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13031,7 +13046,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13237,7 +13252,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13649,7 +13664,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14473,7 +14488,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15091,7 +15106,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15172,7 +15187,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ68">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR68">
         <v>1.04</v>
@@ -15297,7 +15312,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15378,7 +15393,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR69">
         <v>1.21</v>
@@ -15581,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ70">
         <v>0.09</v>
@@ -15787,7 +15802,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ71">
         <v>0.45</v>
@@ -15996,7 +16011,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ72">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
         <v>1.82</v>
@@ -16121,7 +16136,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16327,7 +16342,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16614,7 +16629,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ75">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -16739,7 +16754,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -16817,7 +16832,7 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ76">
         <v>1.55</v>
@@ -17232,7 +17247,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ78">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR78">
         <v>1.59</v>
@@ -17435,7 +17450,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ79">
         <v>0.82</v>
@@ -17847,7 +17862,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
         <v>1.27</v>
@@ -18056,7 +18071,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR82">
         <v>0.92</v>
@@ -18181,7 +18196,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18671,7 +18686,7 @@
         <v>1.4</v>
       </c>
       <c r="AP85">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ85">
         <v>1.27</v>
@@ -18799,7 +18814,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19701,7 +19716,7 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ90">
         <v>0.09</v>
@@ -19829,7 +19844,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19910,7 +19925,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ91">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
         <v>1.77</v>
@@ -20035,7 +20050,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20319,10 +20334,10 @@
         <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR93">
         <v>1.23</v>
@@ -20447,7 +20462,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20528,7 +20543,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR94">
         <v>2.03</v>
@@ -20731,10 +20746,10 @@
         <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ95">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR95">
         <v>1.79</v>
@@ -20859,7 +20874,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21065,7 +21080,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21143,7 +21158,7 @@
         <v>0.2</v>
       </c>
       <c r="AP97">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ97">
         <v>0.82</v>
@@ -21477,7 +21492,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21683,7 +21698,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21889,7 +21904,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22919,7 +22934,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -22997,7 +23012,7 @@
         <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ106">
         <v>0.9</v>
@@ -23125,7 +23140,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23203,7 +23218,7 @@
         <v>1.33</v>
       </c>
       <c r="AP107">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107">
         <v>1.45</v>
@@ -23331,7 +23346,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23412,7 +23427,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR108">
         <v>1.16</v>
@@ -23618,7 +23633,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ109">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR109">
         <v>1.75</v>
@@ -23743,7 +23758,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23824,7 +23839,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR110">
         <v>1.65</v>
@@ -24030,7 +24045,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ111">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24233,7 +24248,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ112">
         <v>1.55</v>
@@ -24361,7 +24376,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24567,7 +24582,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
@@ -24645,7 +24660,7 @@
         <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ114">
         <v>1.5</v>
@@ -25597,7 +25612,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26215,7 +26230,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26293,7 +26308,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
         <v>0.9</v>
@@ -26708,7 +26723,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ124">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -26833,7 +26848,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -26911,7 +26926,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ125">
         <v>1.55</v>
@@ -27120,7 +27135,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
@@ -27245,7 +27260,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27529,7 +27544,7 @@
         <v>1.57</v>
       </c>
       <c r="AP128">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ128">
         <v>1.45</v>
@@ -27657,7 +27672,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27863,7 +27878,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28150,7 +28165,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ131">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28275,7 +28290,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28687,7 +28702,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28765,7 +28780,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134">
         <v>0.92</v>
@@ -29099,7 +29114,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29386,7 +29401,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ137">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR137">
         <v>1.17</v>
@@ -29798,7 +29813,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ139">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR139">
         <v>1.07</v>
@@ -30129,7 +30144,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30207,7 +30222,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ141">
         <v>1.5</v>
@@ -30541,7 +30556,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30619,10 +30634,10 @@
         <v>0.88</v>
       </c>
       <c r="AP143">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ143">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR143">
         <v>1.68</v>
@@ -30747,7 +30762,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30825,10 +30840,10 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ144">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR144">
         <v>1.4</v>
@@ -31159,7 +31174,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31571,7 +31586,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31777,7 +31792,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32064,7 +32079,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ150">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR150">
         <v>1.79</v>
@@ -32395,7 +32410,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32473,7 +32488,7 @@
         <v>1.89</v>
       </c>
       <c r="AP152">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ152">
         <v>1.91</v>
@@ -32682,7 +32697,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ153">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR153">
         <v>1.62</v>
@@ -32807,7 +32822,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32885,7 +32900,7 @@
         <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ154">
         <v>1.55</v>
@@ -33013,7 +33028,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33091,7 +33106,7 @@
         <v>0.7</v>
       </c>
       <c r="AP155">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ155">
         <v>0.92</v>
@@ -33219,7 +33234,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33300,7 +33315,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ156">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR156">
         <v>2.05</v>
@@ -33506,7 +33521,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR157">
         <v>1.54</v>
@@ -33631,7 +33646,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34043,7 +34058,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34121,7 +34136,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ160">
         <v>0.82</v>
@@ -34249,7 +34264,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34661,7 +34676,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34948,7 +34963,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ164">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR164">
         <v>1.79</v>
@@ -35073,7 +35088,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35279,7 +35294,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35691,7 +35706,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36103,7 +36118,7 @@
         <v>115</v>
       </c>
       <c r="P170" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q170">
         <v>2.55</v>
@@ -36309,7 +36324,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36515,7 +36530,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36721,7 +36736,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36878,6 +36893,830 @@
       </c>
       <c r="BP173">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7453593</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45676.39583333334</v>
+      </c>
+      <c r="F174">
+        <v>22</v>
+      </c>
+      <c r="G174" t="s">
+        <v>75</v>
+      </c>
+      <c r="H174" t="s">
+        <v>73</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>2</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174" t="s">
+        <v>87</v>
+      </c>
+      <c r="P174" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q174">
+        <v>4.33</v>
+      </c>
+      <c r="R174">
+        <v>2.25</v>
+      </c>
+      <c r="S174">
+        <v>2.5</v>
+      </c>
+      <c r="T174">
+        <v>1.36</v>
+      </c>
+      <c r="U174">
+        <v>3</v>
+      </c>
+      <c r="V174">
+        <v>2.63</v>
+      </c>
+      <c r="W174">
+        <v>1.44</v>
+      </c>
+      <c r="X174">
+        <v>7</v>
+      </c>
+      <c r="Y174">
+        <v>1.1</v>
+      </c>
+      <c r="Z174">
+        <v>3.94</v>
+      </c>
+      <c r="AA174">
+        <v>3.75</v>
+      </c>
+      <c r="AB174">
+        <v>1.87</v>
+      </c>
+      <c r="AC174">
+        <v>1.03</v>
+      </c>
+      <c r="AD174">
+        <v>13</v>
+      </c>
+      <c r="AE174">
+        <v>1.24</v>
+      </c>
+      <c r="AF174">
+        <v>3.89</v>
+      </c>
+      <c r="AG174">
+        <v>1.78</v>
+      </c>
+      <c r="AH174">
+        <v>1.97</v>
+      </c>
+      <c r="AI174">
+        <v>1.7</v>
+      </c>
+      <c r="AJ174">
+        <v>2.05</v>
+      </c>
+      <c r="AK174">
+        <v>1.87</v>
+      </c>
+      <c r="AL174">
+        <v>1.26</v>
+      </c>
+      <c r="AM174">
+        <v>1.26</v>
+      </c>
+      <c r="AN174">
+        <v>1.3</v>
+      </c>
+      <c r="AO174">
+        <v>1.5</v>
+      </c>
+      <c r="AP174">
+        <v>1.18</v>
+      </c>
+      <c r="AQ174">
+        <v>1.64</v>
+      </c>
+      <c r="AR174">
+        <v>1.38</v>
+      </c>
+      <c r="AS174">
+        <v>1.37</v>
+      </c>
+      <c r="AT174">
+        <v>2.75</v>
+      </c>
+      <c r="AU174">
+        <v>4</v>
+      </c>
+      <c r="AV174">
+        <v>4</v>
+      </c>
+      <c r="AW174">
+        <v>7</v>
+      </c>
+      <c r="AX174">
+        <v>9</v>
+      </c>
+      <c r="AY174">
+        <v>14</v>
+      </c>
+      <c r="AZ174">
+        <v>16</v>
+      </c>
+      <c r="BA174">
+        <v>7</v>
+      </c>
+      <c r="BB174">
+        <v>7</v>
+      </c>
+      <c r="BC174">
+        <v>14</v>
+      </c>
+      <c r="BD174">
+        <v>2.32</v>
+      </c>
+      <c r="BE174">
+        <v>6.75</v>
+      </c>
+      <c r="BF174">
+        <v>1.74</v>
+      </c>
+      <c r="BG174">
+        <v>1.27</v>
+      </c>
+      <c r="BH174">
+        <v>3.3</v>
+      </c>
+      <c r="BI174">
+        <v>1.48</v>
+      </c>
+      <c r="BJ174">
+        <v>2.43</v>
+      </c>
+      <c r="BK174">
+        <v>1.7</v>
+      </c>
+      <c r="BL174">
+        <v>2.05</v>
+      </c>
+      <c r="BM174">
+        <v>2.23</v>
+      </c>
+      <c r="BN174">
+        <v>1.56</v>
+      </c>
+      <c r="BO174">
+        <v>2.9</v>
+      </c>
+      <c r="BP174">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7453590</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45676.5</v>
+      </c>
+      <c r="F175">
+        <v>22</v>
+      </c>
+      <c r="G175" t="s">
+        <v>78</v>
+      </c>
+      <c r="H175" t="s">
+        <v>80</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>1</v>
+      </c>
+      <c r="O175" t="s">
+        <v>113</v>
+      </c>
+      <c r="P175" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q175">
+        <v>2.05</v>
+      </c>
+      <c r="R175">
+        <v>2.25</v>
+      </c>
+      <c r="S175">
+        <v>5.5</v>
+      </c>
+      <c r="T175">
+        <v>1.36</v>
+      </c>
+      <c r="U175">
+        <v>2.87</v>
+      </c>
+      <c r="V175">
+        <v>2.7</v>
+      </c>
+      <c r="W175">
+        <v>1.4</v>
+      </c>
+      <c r="X175">
+        <v>6.75</v>
+      </c>
+      <c r="Y175">
+        <v>1.09</v>
+      </c>
+      <c r="Z175">
+        <v>1.53</v>
+      </c>
+      <c r="AA175">
+        <v>3.8</v>
+      </c>
+      <c r="AB175">
+        <v>6</v>
+      </c>
+      <c r="AC175">
+        <v>1.05</v>
+      </c>
+      <c r="AD175">
+        <v>9.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.28</v>
+      </c>
+      <c r="AF175">
+        <v>3.6</v>
+      </c>
+      <c r="AG175">
+        <v>1.99</v>
+      </c>
+      <c r="AH175">
+        <v>1.85</v>
+      </c>
+      <c r="AI175">
+        <v>1.98</v>
+      </c>
+      <c r="AJ175">
+        <v>1.72</v>
+      </c>
+      <c r="AK175">
+        <v>1.13</v>
+      </c>
+      <c r="AL175">
+        <v>1.22</v>
+      </c>
+      <c r="AM175">
+        <v>2.45</v>
+      </c>
+      <c r="AN175">
+        <v>2.1</v>
+      </c>
+      <c r="AO175">
+        <v>0.73</v>
+      </c>
+      <c r="AP175">
+        <v>2.18</v>
+      </c>
+      <c r="AQ175">
+        <v>0.67</v>
+      </c>
+      <c r="AR175">
+        <v>1.74</v>
+      </c>
+      <c r="AS175">
+        <v>1.23</v>
+      </c>
+      <c r="AT175">
+        <v>2.97</v>
+      </c>
+      <c r="AU175">
+        <v>10</v>
+      </c>
+      <c r="AV175">
+        <v>3</v>
+      </c>
+      <c r="AW175">
+        <v>8</v>
+      </c>
+      <c r="AX175">
+        <v>3</v>
+      </c>
+      <c r="AY175">
+        <v>19</v>
+      </c>
+      <c r="AZ175">
+        <v>7</v>
+      </c>
+      <c r="BA175">
+        <v>6</v>
+      </c>
+      <c r="BB175">
+        <v>2</v>
+      </c>
+      <c r="BC175">
+        <v>8</v>
+      </c>
+      <c r="BD175">
+        <v>1.35</v>
+      </c>
+      <c r="BE175">
+        <v>7.5</v>
+      </c>
+      <c r="BF175">
+        <v>3.45</v>
+      </c>
+      <c r="BG175">
+        <v>1.19</v>
+      </c>
+      <c r="BH175">
+        <v>4.1</v>
+      </c>
+      <c r="BI175">
+        <v>1.33</v>
+      </c>
+      <c r="BJ175">
+        <v>2.95</v>
+      </c>
+      <c r="BK175">
+        <v>1.54</v>
+      </c>
+      <c r="BL175">
+        <v>2.3</v>
+      </c>
+      <c r="BM175">
+        <v>1.89</v>
+      </c>
+      <c r="BN175">
+        <v>1.8</v>
+      </c>
+      <c r="BO175">
+        <v>2.32</v>
+      </c>
+      <c r="BP175">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7453595</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45676.60416666666</v>
+      </c>
+      <c r="F176">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>81</v>
+      </c>
+      <c r="H176" t="s">
+        <v>84</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>2</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>2</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>211</v>
+      </c>
+      <c r="P176" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q176">
+        <v>2.63</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>4.33</v>
+      </c>
+      <c r="T176">
+        <v>1.4</v>
+      </c>
+      <c r="U176">
+        <v>2.75</v>
+      </c>
+      <c r="V176">
+        <v>3</v>
+      </c>
+      <c r="W176">
+        <v>1.36</v>
+      </c>
+      <c r="X176">
+        <v>8</v>
+      </c>
+      <c r="Y176">
+        <v>1.08</v>
+      </c>
+      <c r="Z176">
+        <v>1.91</v>
+      </c>
+      <c r="AA176">
+        <v>3.25</v>
+      </c>
+      <c r="AB176">
+        <v>4</v>
+      </c>
+      <c r="AC176">
+        <v>1.04</v>
+      </c>
+      <c r="AD176">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE176">
+        <v>1.31</v>
+      </c>
+      <c r="AF176">
+        <v>3.32</v>
+      </c>
+      <c r="AG176">
+        <v>2</v>
+      </c>
+      <c r="AH176">
+        <v>1.73</v>
+      </c>
+      <c r="AI176">
+        <v>1.8</v>
+      </c>
+      <c r="AJ176">
+        <v>1.95</v>
+      </c>
+      <c r="AK176">
+        <v>1.27</v>
+      </c>
+      <c r="AL176">
+        <v>1.3</v>
+      </c>
+      <c r="AM176">
+        <v>1.77</v>
+      </c>
+      <c r="AN176">
+        <v>1.4</v>
+      </c>
+      <c r="AO176">
+        <v>0.7</v>
+      </c>
+      <c r="AP176">
+        <v>1.27</v>
+      </c>
+      <c r="AQ176">
+        <v>0.91</v>
+      </c>
+      <c r="AR176">
+        <v>1.54</v>
+      </c>
+      <c r="AS176">
+        <v>0.93</v>
+      </c>
+      <c r="AT176">
+        <v>2.47</v>
+      </c>
+      <c r="AU176">
+        <v>3</v>
+      </c>
+      <c r="AV176">
+        <v>5</v>
+      </c>
+      <c r="AW176">
+        <v>15</v>
+      </c>
+      <c r="AX176">
+        <v>6</v>
+      </c>
+      <c r="AY176">
+        <v>22</v>
+      </c>
+      <c r="AZ176">
+        <v>12</v>
+      </c>
+      <c r="BA176">
+        <v>8</v>
+      </c>
+      <c r="BB176">
+        <v>3</v>
+      </c>
+      <c r="BC176">
+        <v>11</v>
+      </c>
+      <c r="BD176">
+        <v>1.49</v>
+      </c>
+      <c r="BE176">
+        <v>7</v>
+      </c>
+      <c r="BF176">
+        <v>2.9</v>
+      </c>
+      <c r="BG176">
+        <v>1.27</v>
+      </c>
+      <c r="BH176">
+        <v>3.3</v>
+      </c>
+      <c r="BI176">
+        <v>1.48</v>
+      </c>
+      <c r="BJ176">
+        <v>2.45</v>
+      </c>
+      <c r="BK176">
+        <v>1.76</v>
+      </c>
+      <c r="BL176">
+        <v>1.94</v>
+      </c>
+      <c r="BM176">
+        <v>2.18</v>
+      </c>
+      <c r="BN176">
+        <v>1.58</v>
+      </c>
+      <c r="BO176">
+        <v>2.8</v>
+      </c>
+      <c r="BP176">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7453592</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45676.63541666666</v>
+      </c>
+      <c r="F177">
+        <v>22</v>
+      </c>
+      <c r="G177" t="s">
+        <v>82</v>
+      </c>
+      <c r="H177" t="s">
+        <v>77</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>2</v>
+      </c>
+      <c r="K177">
+        <v>3</v>
+      </c>
+      <c r="L177">
+        <v>3</v>
+      </c>
+      <c r="M177">
+        <v>2</v>
+      </c>
+      <c r="N177">
+        <v>5</v>
+      </c>
+      <c r="O177" t="s">
+        <v>212</v>
+      </c>
+      <c r="P177" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q177">
+        <v>2.3</v>
+      </c>
+      <c r="R177">
+        <v>2.4</v>
+      </c>
+      <c r="S177">
+        <v>4.33</v>
+      </c>
+      <c r="T177">
+        <v>1.29</v>
+      </c>
+      <c r="U177">
+        <v>3.5</v>
+      </c>
+      <c r="V177">
+        <v>2.25</v>
+      </c>
+      <c r="W177">
+        <v>1.57</v>
+      </c>
+      <c r="X177">
+        <v>5.5</v>
+      </c>
+      <c r="Y177">
+        <v>1.14</v>
+      </c>
+      <c r="Z177">
+        <v>1.73</v>
+      </c>
+      <c r="AA177">
+        <v>4</v>
+      </c>
+      <c r="AB177">
+        <v>4</v>
+      </c>
+      <c r="AC177">
+        <v>1.02</v>
+      </c>
+      <c r="AD177">
+        <v>19</v>
+      </c>
+      <c r="AE177">
+        <v>1.16</v>
+      </c>
+      <c r="AF177">
+        <v>4.87</v>
+      </c>
+      <c r="AG177">
+        <v>1.53</v>
+      </c>
+      <c r="AH177">
+        <v>2.35</v>
+      </c>
+      <c r="AI177">
+        <v>1.53</v>
+      </c>
+      <c r="AJ177">
+        <v>2.38</v>
+      </c>
+      <c r="AK177">
+        <v>1.23</v>
+      </c>
+      <c r="AL177">
+        <v>1.23</v>
+      </c>
+      <c r="AM177">
+        <v>2.05</v>
+      </c>
+      <c r="AN177">
+        <v>1.7</v>
+      </c>
+      <c r="AO177">
+        <v>0.7</v>
+      </c>
+      <c r="AP177">
+        <v>1.82</v>
+      </c>
+      <c r="AQ177">
+        <v>0.64</v>
+      </c>
+      <c r="AR177">
+        <v>1.71</v>
+      </c>
+      <c r="AS177">
+        <v>1.48</v>
+      </c>
+      <c r="AT177">
+        <v>3.19</v>
+      </c>
+      <c r="AU177">
+        <v>8</v>
+      </c>
+      <c r="AV177">
+        <v>11</v>
+      </c>
+      <c r="AW177">
+        <v>6</v>
+      </c>
+      <c r="AX177">
+        <v>9</v>
+      </c>
+      <c r="AY177">
+        <v>16</v>
+      </c>
+      <c r="AZ177">
+        <v>24</v>
+      </c>
+      <c r="BA177">
+        <v>7</v>
+      </c>
+      <c r="BB177">
+        <v>3</v>
+      </c>
+      <c r="BC177">
+        <v>10</v>
+      </c>
+      <c r="BD177">
+        <v>1.47</v>
+      </c>
+      <c r="BE177">
+        <v>7</v>
+      </c>
+      <c r="BF177">
+        <v>2.95</v>
+      </c>
+      <c r="BG177">
+        <v>1.21</v>
+      </c>
+      <c r="BH177">
+        <v>3.9</v>
+      </c>
+      <c r="BI177">
+        <v>1.36</v>
+      </c>
+      <c r="BJ177">
+        <v>2.8</v>
+      </c>
+      <c r="BK177">
+        <v>1.7</v>
+      </c>
+      <c r="BL177">
+        <v>2.05</v>
+      </c>
+      <c r="BM177">
+        <v>2.05</v>
+      </c>
+      <c r="BN177">
+        <v>1.7</v>
+      </c>
+      <c r="BO177">
+        <v>2.4</v>
+      </c>
+      <c r="BP177">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,9 @@
     <t>['19', '22', '77', '90+5']</t>
   </si>
   <si>
+    <t>['15']</t>
+  </si>
+  <si>
     <t>['2']</t>
   </si>
   <si>
@@ -1510,7 +1513,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2540,7 +2543,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3364,7 +3367,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3776,7 +3779,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3982,7 +3985,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4188,7 +4191,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4600,7 +4603,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5218,7 +5221,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5630,7 +5633,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5836,7 +5839,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6248,7 +6251,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6660,7 +6663,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6866,7 +6869,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7072,7 +7075,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8102,7 +8105,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8308,7 +8311,7 @@
         <v>87</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -8514,7 +8517,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9544,7 +9547,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9750,7 +9753,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10368,7 +10371,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10986,7 +10989,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11192,7 +11195,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11398,7 +11401,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11604,7 +11607,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12634,7 +12637,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13046,7 +13049,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13252,7 +13255,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13664,7 +13667,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14488,7 +14491,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15106,7 +15109,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15312,7 +15315,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16136,7 +16139,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16342,7 +16345,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16754,7 +16757,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -18196,7 +18199,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18814,7 +18817,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19844,7 +19847,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20050,7 +20053,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20462,7 +20465,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20874,7 +20877,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21080,7 +21083,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21492,7 +21495,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21698,7 +21701,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21904,7 +21907,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22934,7 +22937,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23140,7 +23143,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23346,7 +23349,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23758,7 +23761,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24376,7 +24379,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24582,7 +24585,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
@@ -25612,7 +25615,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26230,7 +26233,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26848,7 +26851,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27260,7 +27263,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27672,7 +27675,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27878,7 +27881,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28290,7 +28293,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28702,7 +28705,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29114,7 +29117,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -30144,7 +30147,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30556,7 +30559,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30762,7 +30765,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31174,7 +31177,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31586,7 +31589,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31792,7 +31795,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32410,7 +32413,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32822,7 +32825,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33028,7 +33031,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33234,7 +33237,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33646,7 +33649,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34058,7 +34061,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34264,7 +34267,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34676,7 +34679,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35088,7 +35091,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35294,7 +35297,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35706,7 +35709,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36118,7 +36121,7 @@
         <v>115</v>
       </c>
       <c r="P170" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q170">
         <v>2.55</v>
@@ -36324,7 +36327,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36530,7 +36533,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36736,7 +36739,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36942,7 +36945,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37145,7 +37148,7 @@
         <v>1</v>
       </c>
       <c r="O175" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="P175" t="s">
         <v>87</v>
@@ -37351,10 +37354,10 @@
         <v>3</v>
       </c>
       <c r="O176" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37557,10 +37560,10 @@
         <v>5</v>
       </c>
       <c r="O177" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q177">
         <v>2.3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="295">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['15', '57', '90+7']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1257,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1516,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2543,7 +2546,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2830,7 +2833,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ8">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3367,7 +3370,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3779,7 +3782,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3857,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
         <v>0.92</v>
@@ -3985,7 +3988,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4191,7 +4194,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4603,7 +4606,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5221,7 +5224,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5633,7 +5636,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5839,7 +5842,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6251,7 +6254,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6663,7 +6666,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6869,7 +6872,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -6947,7 +6950,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -7075,7 +7078,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7362,7 +7365,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ30">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR30">
         <v>2.35</v>
@@ -8105,7 +8108,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8311,7 +8314,7 @@
         <v>87</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -8517,7 +8520,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8801,7 +8804,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>1.18</v>
@@ -9547,7 +9550,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9753,7 +9756,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10371,7 +10374,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10452,7 +10455,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ45">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10989,7 +10992,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11195,7 +11198,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11401,7 +11404,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11607,7 +11610,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12097,7 +12100,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53">
         <v>0.67</v>
@@ -12637,7 +12640,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13049,7 +13052,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13255,7 +13258,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13336,7 +13339,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ59">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13667,7 +13670,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14491,7 +14494,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15109,7 +15112,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15315,7 +15318,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16139,7 +16142,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16345,7 +16348,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16757,7 +16760,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -17865,7 +17868,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ81">
         <v>1.27</v>
@@ -18199,7 +18202,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18817,7 +18820,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19104,7 +19107,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ87">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR87">
         <v>1.36</v>
@@ -19847,7 +19850,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20053,7 +20056,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20337,7 +20340,7 @@
         <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ93">
         <v>0.64</v>
@@ -20465,7 +20468,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20877,7 +20880,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21083,7 +21086,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21495,7 +21498,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21701,7 +21704,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21907,7 +21910,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22194,7 +22197,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ102">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR102">
         <v>1.86</v>
@@ -22937,7 +22940,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23015,7 +23018,7 @@
         <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ106">
         <v>0.9</v>
@@ -23143,7 +23146,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23224,7 +23227,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ107">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR107">
         <v>1.5</v>
@@ -23349,7 +23352,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23761,7 +23764,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24379,7 +24382,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24585,7 +24588,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>1.95</v>
@@ -25615,7 +25618,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26233,7 +26236,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26851,7 +26854,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -26929,7 +26932,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ125">
         <v>1.55</v>
@@ -27263,7 +27266,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27550,7 +27553,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ128">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27675,7 +27678,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27881,7 +27884,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28293,7 +28296,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28705,7 +28708,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29117,7 +29120,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29610,7 +29613,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ138">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -30147,7 +30150,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30559,7 +30562,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30765,7 +30768,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30843,7 +30846,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ144">
         <v>1.64</v>
@@ -31177,7 +31180,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31589,7 +31592,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31670,7 +31673,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ148">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR148">
         <v>1.11</v>
@@ -31795,7 +31798,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32413,7 +32416,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32825,7 +32828,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33031,7 +33034,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33237,7 +33240,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33649,7 +33652,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34061,7 +34064,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34139,7 +34142,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ160">
         <v>0.82</v>
@@ -34267,7 +34270,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34679,7 +34682,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35091,7 +35094,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35297,7 +35300,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35378,7 +35381,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ166">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR166">
         <v>1.26</v>
@@ -35709,7 +35712,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36121,7 +36124,7 @@
         <v>115</v>
       </c>
       <c r="P170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q170">
         <v>2.55</v>
@@ -36327,7 +36330,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36533,7 +36536,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36739,7 +36742,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36945,7 +36948,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37357,7 +37360,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37435,7 +37438,7 @@
         <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ176">
         <v>0.91</v>
@@ -37563,7 +37566,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37720,6 +37723,212 @@
       </c>
       <c r="BP177">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7453602</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45681.69791666666</v>
+      </c>
+      <c r="F178">
+        <v>23</v>
+      </c>
+      <c r="G178" t="s">
+        <v>81</v>
+      </c>
+      <c r="H178" t="s">
+        <v>82</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>2</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>2</v>
+      </c>
+      <c r="O178" t="s">
+        <v>214</v>
+      </c>
+      <c r="P178" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q178">
+        <v>3.4</v>
+      </c>
+      <c r="R178">
+        <v>2.2</v>
+      </c>
+      <c r="S178">
+        <v>3.1</v>
+      </c>
+      <c r="T178">
+        <v>1.36</v>
+      </c>
+      <c r="U178">
+        <v>3</v>
+      </c>
+      <c r="V178">
+        <v>2.75</v>
+      </c>
+      <c r="W178">
+        <v>1.4</v>
+      </c>
+      <c r="X178">
+        <v>7</v>
+      </c>
+      <c r="Y178">
+        <v>1.1</v>
+      </c>
+      <c r="Z178">
+        <v>2.8</v>
+      </c>
+      <c r="AA178">
+        <v>3.5</v>
+      </c>
+      <c r="AB178">
+        <v>2.34</v>
+      </c>
+      <c r="AC178">
+        <v>1.05</v>
+      </c>
+      <c r="AD178">
+        <v>12</v>
+      </c>
+      <c r="AE178">
+        <v>1.28</v>
+      </c>
+      <c r="AF178">
+        <v>3.52</v>
+      </c>
+      <c r="AG178">
+        <v>1.8</v>
+      </c>
+      <c r="AH178">
+        <v>1.94</v>
+      </c>
+      <c r="AI178">
+        <v>1.67</v>
+      </c>
+      <c r="AJ178">
+        <v>2.1</v>
+      </c>
+      <c r="AK178">
+        <v>1.55</v>
+      </c>
+      <c r="AL178">
+        <v>1.29</v>
+      </c>
+      <c r="AM178">
+        <v>1.41</v>
+      </c>
+      <c r="AN178">
+        <v>1.27</v>
+      </c>
+      <c r="AO178">
+        <v>1.45</v>
+      </c>
+      <c r="AP178">
+        <v>1.25</v>
+      </c>
+      <c r="AQ178">
+        <v>1.42</v>
+      </c>
+      <c r="AR178">
+        <v>1.57</v>
+      </c>
+      <c r="AS178">
+        <v>1.23</v>
+      </c>
+      <c r="AT178">
+        <v>2.8</v>
+      </c>
+      <c r="AU178">
+        <v>5</v>
+      </c>
+      <c r="AV178">
+        <v>2</v>
+      </c>
+      <c r="AW178">
+        <v>14</v>
+      </c>
+      <c r="AX178">
+        <v>14</v>
+      </c>
+      <c r="AY178">
+        <v>21</v>
+      </c>
+      <c r="AZ178">
+        <v>18</v>
+      </c>
+      <c r="BA178">
+        <v>3</v>
+      </c>
+      <c r="BB178">
+        <v>9</v>
+      </c>
+      <c r="BC178">
+        <v>12</v>
+      </c>
+      <c r="BD178">
+        <v>2.08</v>
+      </c>
+      <c r="BE178">
+        <v>6.75</v>
+      </c>
+      <c r="BF178">
+        <v>1.88</v>
+      </c>
+      <c r="BG178">
+        <v>1.24</v>
+      </c>
+      <c r="BH178">
+        <v>3.55</v>
+      </c>
+      <c r="BI178">
+        <v>1.43</v>
+      </c>
+      <c r="BJ178">
+        <v>2.55</v>
+      </c>
+      <c r="BK178">
+        <v>1.7</v>
+      </c>
+      <c r="BL178">
+        <v>2.05</v>
+      </c>
+      <c r="BM178">
+        <v>2.1</v>
+      </c>
+      <c r="BN178">
+        <v>1.64</v>
+      </c>
+      <c r="BO178">
+        <v>2.65</v>
+      </c>
+      <c r="BP178">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>
